--- a/ProblemList.xlsx
+++ b/ProblemList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rupesh\Desktop\Code\irs\irs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD4CD2E-438F-4FAF-9B8E-261F1EAA1DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004E6D99-6054-4F4A-902C-3DAE842AFA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{483C8F2D-AF51-4A1C-B9C1-330F56817E95}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{483C8F2D-AF51-4A1C-B9C1-330F56817E95}"/>
   </bookViews>
   <sheets>
     <sheet name="Problems" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Problems!$A$1:$G$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="788">
   <si>
     <t>title</t>
   </si>
@@ -10305,6 +10304,70 @@
   </si>
   <si>
     <t>combination</t>
+  </si>
+  <si>
+    <t>Palindrome Partitioning II</t>
+  </si>
+  <si>
+    <t>palindrome-parititioning-2</t>
+  </si>
+  <si>
+    <t>Given a string s, partition s such that every substring of the partition is a palindrome.
+Return the minimum cuts needed for a palindrome partitioning of s.
+Example 1:
+Input: s = "aab"
+Output: 1
+Explanation: The palindrome partitioning ["aa","b"] could be produced using 1 cut.
+Example 2:
+Input: s = "a"
+Output: 0
+Example 3:
+Input: s = "ab"
+Output: 1
+Constraints:
+1 &lt;= s.length &lt;= 2000
+s consists of lowercase English letters only.</t>
+  </si>
+  <si>
+    <t>class Solution {
+    Integer[][] dp;
+    public int minCut(String s) {
+        dp = new Integer[s.length()][s.length()];
+        return recur(s,0, s.length()-1);
+    }
+    public int recur(String s, int i, int j){
+        if( i &gt;= j){
+            dp[i][j] =0;
+            return 0;
+        }
+        if(ifPali(i,j,s)){
+            dp[i][j]  =0;
+            return 0;
+        }
+        if(dp[i][j] != null){
+            return dp[i][j];
+        }
+        int min = Integer.MAX_VALUE;
+        for(int k=i;k&lt;=j;k++){
+            if(ifPali(i,k,s)){
+                int temp = 1 + recur(s,k+1,j);
+                min = Math.min(min,temp);
+            }
+        }
+        dp[i][j] = min;
+        return dp[i][j];
+    }
+    public boolean ifPali(int start, int end, String s){
+        while(start &lt;= end){
+            if(s.charAt(start) != s.charAt(end)){
+                return false;
+            }
+            start++;
+            end--;
+        }
+        return true;
+    }
+}</t>
   </si>
 </sst>
 </file>
@@ -10690,7 +10753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E3BD94-688A-45B7-B301-FA3F55251082}">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" customWidth="1"/>
@@ -14872,6 +14935,29 @@
       </c>
       <c r="G182" s="1" t="s">
         <v>781</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>784</v>
+      </c>
+      <c r="B183" t="s">
+        <v>785</v>
+      </c>
+      <c r="C183" t="s">
+        <v>292</v>
+      </c>
+      <c r="D183" t="s">
+        <v>92</v>
+      </c>
+      <c r="E183" t="s">
+        <v>292</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>

--- a/ProblemList.xlsx
+++ b/ProblemList.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004E6D99-6054-4F4A-902C-3DAE842AFA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{483C8F2D-AF51-4A1C-B9C1-330F56817E95}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{483C8F2D-AF51-4A1C-B9C1-330F56817E95}"/>
   </bookViews>
   <sheets>
     <sheet name="Problems" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Problems!$A$1:$G$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/ProblemList.xlsx
+++ b/ProblemList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rupesh\Desktop\Code\irs\irs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004E6D99-6054-4F4A-902C-3DAE842AFA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CB3C71-AA8A-4D6C-90EF-D1FABAB94B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{483C8F2D-AF51-4A1C-B9C1-330F56817E95}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Problems!$A$1:$G$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="793">
   <si>
     <t>title</t>
   </si>
@@ -10367,6 +10366,71 @@
             end--;
         }
         return true;
+    }
+}</t>
+  </si>
+  <si>
+    <t>Shortest Path Visiting All Nodes</t>
+  </si>
+  <si>
+    <t>shortest-path-visiting-all-nodes</t>
+  </si>
+  <si>
+    <t>Graph,Bit-mask</t>
+  </si>
+  <si>
+    <t>You have an undirected, connected graph of n nodes labeled from 0 to n - 1. You are given an array graph where graph[i] is a list of all the nodes connected with node i by an edge.
+Return the length of the shortest path that visits every node. You may start and stop at any node, you may revisit nodes multiple times, and you may reuse edges.
+Example 1:
+Input: graph = [[1,2,3],[0],[0],[0]]
+Output: 4
+Explanation: One possible path is [1,0,2,0,3]
+Example 2:
+Input: graph = [[1],[0,2,4],[1,3,4],[2],[1,2]]
+Output: 4
+Explanation: One possible path is [0,1,4,2,3]
+Constraints:
+n == graph.length
+1 &lt;= n &lt;= 12
+0 &lt;= graph[i].length &lt; n
+graph[i] does not contain i.
+If graph[a] contains b, then graph[b] contains a.
+The input graph is always connected.</t>
+  </si>
+  <si>
+    <t>class Solution {
+    public int shortestPathLength(int[][] graph) {
+        int n = graph.length;
+        Queue&lt;int[]&gt; queue = new LinkedList&lt;&gt;();
+        boolean[][] visited = new boolean[n][1&lt;&lt;n];
+        for(int i=0;i&lt;n;i++){
+            int mask = 1 &lt;&lt; i;
+            queue.add(new int[]{i,mask});
+            visited[i][mask] = true;
+        }
+        int steps =0;
+        while(!queue.isEmpty()){
+            int size = queue.size();
+            for (int i = 0; i &lt; size; i++) {
+                int[] curr = queue.poll();
+                int node = curr[0];
+                int mask = curr[1];
+                // If all nodes visited → done
+                if (mask == (1 &lt;&lt; n) - 1) {
+                    return steps;
+                }
+                // Explore neighbors
+                for (int neighbor : graph[node]) {
+                    int newMask = mask | (1 &lt;&lt; neighbor);
+                    if (!visited[neighbor][newMask]) {
+                        visited[neighbor][newMask] = true;
+                        queue.offer(new int[]{neighbor, newMask});
+                    }
+                }
+            }
+            steps++;
+        }
+        return -1;
     }
 }</t>
   </si>
@@ -10754,7 +10818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E3BD94-688A-45B7-B301-FA3F55251082}">
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" customWidth="1"/>
@@ -14959,6 +15023,29 @@
       </c>
       <c r="G183" s="1" t="s">
         <v>787</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>788</v>
+      </c>
+      <c r="B184" t="s">
+        <v>789</v>
+      </c>
+      <c r="C184" t="s">
+        <v>186</v>
+      </c>
+      <c r="D184" t="s">
+        <v>92</v>
+      </c>
+      <c r="E184" t="s">
+        <v>790</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>792</v>
       </c>
     </row>
   </sheetData>

--- a/ProblemList.xlsx
+++ b/ProblemList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rupesh\Desktop\Code\irs\irs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CB3C71-AA8A-4D6C-90EF-D1FABAB94B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7206B3-652C-4C38-8001-71D286E81801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{483C8F2D-AF51-4A1C-B9C1-330F56817E95}"/>
   </bookViews>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="820">
   <si>
     <t>title</t>
   </si>
@@ -6972,9 +6970,6 @@
     <t>leftmost-column-least-one</t>
   </si>
   <si>
-    <t>Escape the Spreading Fire</t>
-  </si>
-  <si>
     <t>Evaluate Division</t>
   </si>
   <si>
@@ -10433,6 +10428,603 @@
         return -1;
     }
 }</t>
+  </si>
+  <si>
+    <t>class Unionfind {
+    int[] parent;
+    int[] size;
+    public Unionfind(int n) {
+        parent = new int[n];
+        size = new int[n];
+        for (int i = 0; i &lt; n; i++) {
+            parent[i] = i;
+            size[i] = 1;
+        }
+    }
+    public int findParent(int a) {
+        if (parent[a] == a) {
+            return a;
+        }
+        parent[a] = findParent(parent[a]); // path compression
+        return parent[a];
+    }
+    public boolean union(int x, int y) {
+        int parentX = findParent(x);
+        int parentY = findParent(y);
+        if (parentX == parentY) {
+            return false;
+        }
+        // union by size
+        if (size[parentX] &gt;= size[parentY]) {
+            parent[parentY] = parentX;
+            size[parentX] += size[parentY];
+        } else {
+            parent[parentX] = parentY;
+            size[parentY] += size[parentX];
+        }
+        return true;
+    }
+}
+class Solution {
+    int[][] directions = {
+        {1, 0},
+        {-1, 0},
+        {0, 1},
+        {0, -1}
+    };
+    public List&lt;Integer&gt; numIslands2(int m, int n, int[][] positions) {
+        List&lt;Integer&gt; output = new ArrayList&lt;&gt;();
+        Unionfind uf = new Unionfind(m * n);
+        boolean[][] land = new boolean[m][n];
+        int count = 0;
+        for (int[] item : positions) {
+            int row = item[0];
+            int col = item[1];
+            // duplicate position
+            if (land[row][col]) {
+                output.add(count);
+                continue;
+            }
+            land[row][col] = true;
+            count++;
+            int currentCell = row * n + col;
+            for (int[] dir : directions) {
+                int newRow = row + dir[0];
+                int newCol = col + dir[1];
+                if (newRow &lt; 0 || newCol &lt; 0 ||
+                    newRow &gt;= m || newCol &gt;= n ||
+                    !land[newRow][newCol]) {
+                    continue;
+                }
+                int neighborCell = newRow * n + newCol;
+                // if merged successfully, islands reduce
+                if (uf.union(currentCell, neighborCell)) {
+                    count--;
+                }
+            }
+            output.add(count);
+        }
+        return output;
+    }
+}</t>
+  </si>
+  <si>
+    <t>Number of Islands II</t>
+  </si>
+  <si>
+    <t>number-of-islands-2</t>
+  </si>
+  <si>
+    <t>You are given an empty 2D binary grid grid of size m x n. The grid represents a map where 0's represent water and 1's represent land. Initially, all the cells of grid are water cells (i.e., all the cells are 0's).
+We may perform an add land operation which turns the water at position into a land. You are given an array positions where positions[i] = [ri, ci] is the position (ri, ci) at which we should operate the ith operation.
+Return an array of integers answer where answer[i] is the number of islands after turning the cell (ri, ci) into a land.
+An island is surrounded by water and is formed by connecting adjacent lands horizontally or vertically. You may assume all four edges of the grid are all surrounded by water.
+Example 1:
+Input: m = 3, n = 3, positions = [[0,0],[0,1],[1,2],[2,1]]
+Output: [1,1,2,3]
+Explanation:
+Initially, the 2d grid is filled with water.
+- Operation #1: addLand(0, 0) turns the water at grid[0][0] into a land. We have 1 island.
+- Operation #2: addLand(0, 1) turns the water at grid[0][1] into a land. We still have 1 island.
+- Operation #3: addLand(1, 2) turns the water at grid[1][2] into a land. We have 2 islands.
+- Operation #4: addLand(2, 1) turns the water at grid[2][1] into a land. We have 3 islands.
+Example 2:
+Input: m = 1, n = 1, positions = [[0,0]]
+Output: [1]</t>
+  </si>
+  <si>
+    <t>The Earliest Moment When Everyone Become Friends</t>
+  </si>
+  <si>
+    <t>earliest-moment-when-everyone-friends</t>
+  </si>
+  <si>
+    <t>There are n people in a social group labeled from 0 to n - 1. You are given an array logs where logs[i] = [timestampi, xi, yi] indicates that xi and yi will be friends at the time timestampi.
+Friendship is symmetric. That means if a is friends with b, then b is friends with a. Also, person a is acquainted with a person b if a is friends with b, or a is a friend of someone acquainted with b.
+Return the earliest time for which every person became acquainted with every other person. If there is no such earliest time, return -1.
+Example 1:
+Input: logs = [[20190101,0,1],[20190104,3,4],[20190107,2,3],[20190211,1,5],[20190224,2,4],[20190301,0,3],[20190312,1,2],[20190322,4,5]], n = 6
+Output: 20190301
+Explanation: 
+The first event occurs at timestamp = 20190101, and after 0 and 1 become friends, we have the following friendship groups [0,1], [2], [3], [4], [5].
+The second event occurs at timestamp = 20190104, and after 3 and 4 become friends, we have the following friendship groups [0,1], [2], [3,4], [5].
+The third event occurs at timestamp = 20190107, and after 2 and 3 become friends, we have the following friendship groups [0,1], [2,3,4], [5].
+The fourth event occurs at timestamp = 20190211, and after 1 and 5 become friends, we have the following friendship groups [0,1,5], [2,3,4].
+The fifth event occurs at timestamp = 20190224, and as 2 and 4 are already friends, nothing happens.
+The sixth event occurs at timestamp = 20190301, and after 0 and 3 become friends, we all become friends.
+Example 2:
+Input: logs = [[0,2,0],[1,0,1],[3,0,3],[4,1,2],[7,3,1]], n = 4
+Output: 3
+Explanation: At timestamp = 3, all the persons (i.e., 0, 1, 2, and 3) become friends.
+Constraints:
+2 &lt;= n &lt;= 100
+1 &lt;= logs.length &lt;= 104
+logs[i].length == 3
+0 &lt;= timestampi &lt;= 109
+0 &lt;= xi, yi &lt;= n - 1
+xi != yi
+All the values timestampi are unique.
+All the pairs (xi, yi) occur at most one time in the input.</t>
+  </si>
+  <si>
+    <t>class UnionFind {
+    int[] parent;
+    int[] size;
+    public UnionFind(int n) {
+        parent = new int[n];
+        size = new int[n];
+        for (int i = 0; i &lt; n; i++) {
+            parent[i] = i;
+            size[i] = 1;
+        }
+    }
+    public int findParent(int x) {
+        if (parent[x] == x) {
+            return x;
+        }
+        parent[x] = findParent(parent[x]); // path compression
+        return parent[x];
+    }
+    public boolean union(int x, int y) {
+        int parentX = findParent(x);
+        int parentY = findParent(y);
+        // already connected
+        if (parentX == parentY) {
+            return false;
+        }
+        // union by size
+        if (size[parentX] &gt;= size[parentY]) {
+            parent[parentY] = parentX;
+            size[parentX] += size[parentY];
+        } else {
+            parent[parentX] = parentY;
+            size[parentY] += size[parentX];
+        }
+        return true;
+    }
+}
+class Solution {
+    public int earliestAcq(int[][] logs, int n) {
+        // sort by timestamp
+        Arrays.sort(logs, (a, b) -&gt; a[0] - b[0]);
+        UnionFind uf = new UnionFind(n);
+        int components = n;
+        for (int[] log : logs) {
+            int timestamp = log[0];
+            int personA = log[1];
+            int personB = log[2];
+            // if merged successfully
+            if (uf.union(personA, personB)) {
+                components--;
+            }
+            // everyone connected
+            if (components == 1) {
+                return timestamp;
+            }
+        }
+        return -1;
+    }
+}</t>
+  </si>
+  <si>
+    <t>First Unique Number</t>
+  </si>
+  <si>
+    <t>first-unique-number</t>
+  </si>
+  <si>
+    <t>You have a queue of integers, you need to retrieve the first unique integer in the queue.
+Implement the FirstUnique class:
+FirstUnique(int[] nums) Initializes the object with the numbers in the queue.
+int showFirstUnique() returns the value of the first unique integer of the queue, and returns -1 if there is no such integer.
+void add(int value) insert value to the queue.
+Example 1:
+Input: 
+["FirstUnique","showFirstUnique","add","showFirstUnique","add","showFirstUnique","add","showFirstUnique"]
+[[[2,3,5]],[],[5],[],[2],[],[3],[]]
+Output: 
+[null,2,null,2,null,3,null,-1]
+Explanation: 
+FirstUnique firstUnique = new FirstUnique([2,3,5]);
+firstUnique.showFirstUnique(); // return 2
+firstUnique.add(5);            // the queue is now [2,3,5,5]
+firstUnique.showFirstUnique(); // return 2
+firstUnique.add(2);            // the queue is now [2,3,5,5,2]
+firstUnique.showFirstUnique(); // return 3
+firstUnique.add(3);            // the queue is now [2,3,5,5,2,3]
+firstUnique.showFirstUnique(); // return -1
+Example 2:
+Input: 
+["FirstUnique","showFirstUnique","add","add","add","add","add","showFirstUnique"]
+[[[7,7,7,7,7,7]],[],[7],[3],[3],[7],[17],[]]
+Output: 
+[null,-1,null,null,null,null,null,17]
+Explanation: 
+FirstUnique firstUnique = new FirstUnique([7,7,7,7,7,7]);
+firstUnique.showFirstUnique(); // return -1
+firstUnique.add(7);            // the queue is now [7,7,7,7,7,7,7]
+firstUnique.add(3);            // the queue is now [7,7,7,7,7,7,7,3]
+firstUnique.add(3);            // the queue is now [7,7,7,7,7,7,7,3,3]
+firstUnique.add(7);            // the queue is now [7,7,7,7,7,7,7,3,3,7]
+firstUnique.add(17);           // the queue is now [7,7,7,7,7,7,7,3,3,7,17]
+firstUnique.showFirstUnique(); // return 17
+Example 3:
+Input: 
+["FirstUnique","showFirstUnique","add","showFirstUnique"]
+[[[809]],[],[809],[]]
+Output: 
+[null,809,null,-1]
+Explanation: 
+FirstUnique firstUnique = new FirstUnique([809]);
+firstUnique.showFirstUnique(); // return 809
+firstUnique.add(809);          // the queue is now [809,809]
+firstUnique.showFirstUnique(); // return -1</t>
+  </si>
+  <si>
+    <t>class FirstUnique {
+  private Queue&lt;Integer&gt; queue = new ArrayDeque&lt;&gt;();
+  private Map&lt;Integer, Boolean&gt; isUnique = new HashMap&lt;&gt;();
+  public FirstUnique(int[] nums) {
+    for (int num : nums) {
+      // Notice that we're calling the "add" method of FirstUnique; not of the queue. 
+      this.add(num);
+    }
+  }
+  public int showFirstUnique() {
+    // We need to start by "cleaning" the queue of any non-uniques at the start.
+    // Note that we know that if a value is in the queue, then it is also in
+    // isUnique, as the implementation of add() guarantees this.
+    while (!queue.isEmpty() &amp;&amp; !isUnique.get(queue.peek())) {
+      queue.remove();
+    }
+    // Check if there is still a value left in the queue. There might be no uniques.
+    if (!queue.isEmpty()) {
+      return queue.peek(); // We don't want to actually *remove* the value.
+    }
+    return -1;
+  }
+  public void add(int value) {
+    // Case 1: We need to add the number to the queue and mark it as unique. 
+    if (!isUnique.containsKey(value)) {
+      isUnique.put(value, true);
+      queue.add(value);
+    // Case 2 and 3: We need to mark the number as no longer unique.
+    } else {
+      isUnique.put(value, false);
+    }
+  }
+}</t>
+  </si>
+  <si>
+    <t>Maximum Number of Points From Grid Queries</t>
+  </si>
+  <si>
+    <t>maximum-number-of-points-from-grid</t>
+  </si>
+  <si>
+    <t>You are given an m x n integer matrix grid and an array queries of size k.
+Find an array answer of size k such that for each integer queries[i] you start in the top left cell of the matrix and repeat the following process:
+If queries[i] is strictly greater than the value of the current cell that you are in, then you get one point if it is your first time visiting this cell, and you can move to any adjacent cell in all 4 directions: up, down, left, and right.
+Otherwise, you do not get any points, and you end this process.
+After the process, answer[i] is the maximum number of points you can get. Note that for each query you are allowed to visit the same cell multiple times.
+Return the resulting array answer.
+Example 1:
+Input: grid = [[1,2,3],[2,5,7],[3,5,1]], queries = [5,6,2]
+Output: [5,8,1]
+Explanation: The diagrams above show which cells we visit to get points for each query.
+Example 2:
+Input: grid = [[5,2,1],[1,1,2]], queries = [3]
+Output: [0]
+Explanation: We can not get any points because the value of the top left cell is already greater than or equal to 3.
+Constraints:
+m == grid.length
+n == grid[i].length
+2 &lt;= m, n &lt;= 1000
+4 &lt;= m * n &lt;= 105
+k == queries.length
+1 &lt;= k &lt;= 104
+1 &lt;= grid[i][j], queries[i] &lt;= 106</t>
+  </si>
+  <si>
+    <t>class Solution {
+    public int[] maxPoints(int[][] grid, int[] queries) {
+        int n = grid.length;
+        int m = grid[0].length;
+        int k = queries.length;
+        int[][] q = new int[k][2];
+        for(int i = 0; i &lt; k; i++) {
+            q[i][0] = queries[i];
+            q[i][1] = i;
+        }
+        Arrays.sort(q, (a,b) -&gt; a[0] - b[0]);
+        int[] ans = new int[k];
+        PriorityQueue&lt;int[]&gt; pq = new PriorityQueue&lt;&gt;((a,b) -&gt; a[0] - b[0]);
+        boolean[][] visited = new boolean[n][m];
+        pq.offer(new int[]{grid[0][0], 0, 0});
+        visited[0][0] = true;
+        int count = 0;
+        int[][] dir = {
+            {-1,0},
+            {1,0},
+            {0,-1},
+            {0,1}
+        };
+        for(int[] query : q) {
+            int val = query[0];
+            int idx = query[1];
+            while(!pq.isEmpty() &amp;&amp; pq.peek()[0] &lt; val) {
+                int[] curr = pq.poll();
+                int r = curr[1];
+                int c = curr[2];
+                count++;
+                for(int[] d : dir) {
+                    int nr = r + d[0];
+                    int nc = c + d[1];
+                    if(nr &gt;= 0 &amp;&amp; nc &gt;= 0 &amp;&amp; nr &lt; n &amp;&amp; nc &lt; m &amp;&amp; !visited[nr][nc]) {
+                        visited[nr][nc] = true;
+                        pq.offer(new int[]{grid[nr][nc],nr,nc});
+                    }
+                }
+            }
+            ans[idx] = count;
+        }
+        return ans;
+    }
+}</t>
+  </si>
+  <si>
+    <t>Maximum Candies You Can Get from Boxes</t>
+  </si>
+  <si>
+    <t>Maximum Profit in Job Scheduling</t>
+  </si>
+  <si>
+    <t>We have n jobs, where every job is scheduled to be done from startTime[i] to endTime[i], obtaining a profit of profit[i].
+You're given the startTime, endTime and profit arrays, return the maximum profit you can take such that there are no two jobs in the subset with overlapping time range.
+If you choose a job that ends at time X you will be able to start another job that starts at time X.
+Example 1:
+Input: startTime = [1,2,3,3], endTime = [3,4,5,6], profit = [50,10,40,70]
+Output: 120
+Explanation: The subset chosen is the first and fourth job. 
+Time range [1-3]+[3-6] , we get profit of 120 = 50 + 70.
+Example 2:
+Input: startTime = [1,2,3,4,6], endTime = [3,5,10,6,9], profit = [20,20,100,70,60]
+Output: 150
+Explanation: The subset chosen is the first, fourth and fifth job. 
+Profit obtained 150 = 20 + 70 + 60.
+Example 3:
+Input: startTime = [1,1,1], endTime = [2,3,4], profit = [5,6,4]
+Output: 6
+Constraints:
+1 &lt;= startTime.length == endTime.length == profit.length &lt;= 5 * 104
+1 &lt;= startTime[i] &lt; endTime[i] &lt;= 109
+1 &lt;= profit[i] &lt;= 104</t>
+  </si>
+  <si>
+    <t>class Solution {
+    Map&lt;Integer,Integer&gt; hm = null;
+    public int jobScheduling(int[] startTime, int[] endTime, int[] profit) {
+        int[][] jobs = new int[startTime.length][3];
+        for(int i=0;i&lt;startTime.length;i++){
+            jobs[i] = new int[]{startTime[i],endTime[i],profit[i]};
+        }
+        Arrays.sort(jobs, (a,b) -&gt; a[0] - b[0]);
+        hm = new HashMap&lt;&gt;();
+        return dfs(0,jobs);
+    }
+    public int dfs(int curr, int[][] jobs){
+        if(curr &gt;= jobs.length)
+            return 0;
+        if(hm.containsKey(curr))
+            return hm.get(curr);
+        int next = findNext(curr,jobs);
+        int includeCurr = jobs[curr][2] + ((next == -1) ? 0 : dfs(next,jobs));
+        int excludeCurr = dfs(curr+1,jobs);
+        int max = Math.max(includeCurr,excludeCurr);
+        hm.put(curr,max);
+        return max;
+    }
+    public int findNext(int curr, int[][] jobs){
+        int left = curr + 1;
+        int right = jobs.length - 1;
+        int ans = -1;
+        while(left &lt;= right){
+            int mid = left + (right - left) / 2;
+            if(jobs[mid][0] &gt;= jobs[curr][1]){
+                ans = mid;
+                right = mid - 1;
+            }else{
+                left = mid + 1;
+            }
+        }
+        return ans;
+    }
+}</t>
+  </si>
+  <si>
+    <t>You have n boxes labeled from 0 to n - 1. You are given four arrays: status, candies, keys, and containedBoxes where:
+status[i] is 1 if the ith box is open and 0 if the ith box is closed,
+candies[i] is the number of candies in the ith box,
+keys[i] is a list of the labels of the boxes you can open after opening the ith box.
+containedBoxes[i] is a list of the boxes you found inside the ith box.
+You are given an integer array initialBoxes that contains the labels of the boxes you initially have. You can take all the candies in any open box and you can use the keys in it to open new boxes and you also can use the boxes you find in it.
+Return the maximum number of candies you can get following the rules above.
+Example 1:
+Input: status = [1,0,1,0], candies = [7,5,4,100], keys = [[],[],[1],[]], containedBoxes = [[1,2],[3],[],[]], initialBoxes = [0]
+Output: 16
+Explanation: You will be initially given box 0. You will find 7 candies in it and boxes 1 and 2.
+Box 1 is closed and you do not have a key for it so you will open box 2. You will find 4 candies and a key to box 1 in box 2.
+In box 1, you will find 5 candies and box 3 but you will not find a key to box 3 so box 3 will remain closed.
+Total number of candies collected = 7 + 4 + 5 = 16 candy.
+Example 2:
+Input: status = [1,0,0,0,0,0], candies = [1,1,1,1,1,1], keys = [[1,2,3,4,5],[],[],[],[],[]], containedBoxes = [[1,2,3,4,5],[],[],[],[],[]], initialBoxes = [0]
+Output: 6
+Explanation: You have initially box 0. Opening it you can find boxes 1,2,3,4 and 5 and their keys.
+The total number of candies will be 6.
+Constraints:
+n == status.length == candies.length == keys.length == containedBoxes.length
+1 &lt;= n &lt;= 1000
+status[i] is either 0 or 1.
+1 &lt;= candies[i] &lt;= 1000
+0 &lt;= keys[i].length &lt;= n
+0 &lt;= keys[i][j] &lt; n
+All values of keys[i] are unique.
+0 &lt;= containedBoxes[i].length &lt;= n
+0 &lt;= containedBoxes[i][j] &lt; n
+All values of containedBoxes[i] are unique.
+Each box is contained in one box at most.
+0 &lt;= initialBoxes.length &lt;= n
+0 &lt;= initialBoxes[i] &lt; n</t>
+  </si>
+  <si>
+    <t>class Box {
+    int status;
+    int candies;
+    int[] boxes;
+    int[] keys;
+}
+class Solution {
+    public int maxCandies(int[] status, int[] candies, int[][] keys, int[][] containedBoxes, int[] initialBoxes) {
+        int n = status.length;
+        List&lt;Box&gt; list = new ArrayList&lt;&gt;();
+        for(int i=0;i&lt;n;i++){
+            Box box = new Box();
+            box.status = status[i];
+            box.candies = candies[i];
+            box.boxes = containedBoxes[i];
+            box.keys = keys[i];
+            list.add(box);
+        }
+        Queue&lt;Integer&gt; q = new LinkedList&lt;&gt;();
+        HashSet&lt;Integer&gt; k = new HashSet&lt;&gt;();
+        HashSet&lt;Integer&gt; visited = new HashSet&lt;&gt;();
+        HashSet&lt;Integer&gt; noKey = new HashSet&lt;&gt;();
+        for(int i : initialBoxes){
+            q.add(i);
+            visited.add(i);
+        }
+        int count =0;
+        while(!q.isEmpty()){
+            //System.out.println("Boxes avaiable "+q);
+            int curr = q.poll();
+            Box b = list.get(curr);
+            if(b.status == 0 &amp;&amp; !k.contains(curr)){
+                noKey.add(curr);
+                //System.out.println("Key not available "+curr);
+                continue;
+            }
+            count = b.candies + count;
+            for(int i : b.boxes){
+                if(!visited.contains(i)){
+                    visited.add(i);
+                    q.add(i);
+                }
+            }
+            for(int i : b.keys){
+                k.add(i);
+                if(noKey.remove(i)){ // remove from waiting set
+                    q.add(i);
+                }
+            }
+        }
+        return count;
+    }
+}</t>
+  </si>
+  <si>
+    <t>class Solution {
+    public String findSmallestRegion(List&lt;List&lt;String&gt;&gt; regions, String region1, String region2) {
+        HashMap&lt;String, String&gt; childToParent = new HashMap&lt;&gt;();
+        for(int i=0;i&lt;regions.size();i++){
+            String parent = regions.get(i).get(0);
+            for(int j=1;j&lt;regions.get(i).size();j++){
+                childToParent.put(regions.get(i).get(j),parent);
+            }
+        }
+        // get path
+        List&lt;String&gt; p1 = getPath(childToParent, region1);
+        List&lt;String&gt; p2 = getPath(childToParent, region2);
+        int i=0,j=0;
+        String lowestCommonAncestor = "";
+        while(i &lt; p1.size() &amp;&amp; j &lt; p2.size() &amp;&amp; p1.get(i).equals(p2.get(j))){
+            lowestCommonAncestor = p1.get(i);
+            i++;
+            j++;   
+        }
+        return lowestCommonAncestor;
+    }
+    public List&lt;String&gt; getPath(HashMap&lt;String,String&gt; map, String region){
+        List&lt;String&gt; output = new ArrayList&lt;&gt;();
+        output.add(region);
+        while(map.containsKey(region)){
+            String parent = map.get(region);
+            output.add(parent);
+            region = parent;
+        }
+        Collections.reverse(output);
+        return output;
+    }
+}</t>
+  </si>
+  <si>
+    <t>Smallest Common Region</t>
+  </si>
+  <si>
+    <t>You are given some lists of regions where the first region of each list directly contains all other regions in that list.
+If a region x contains a region y directly, and region y contains region z directly, then region x is said to contain region z indirectly. Note that region x also indirectly contains all regions indirectly containd in y.
+Naturally, if a region x contains (either directly or indirectly) another region y, then x is bigger than or equal to y in size. Also, by definition, a region x contains itself.
+Given two regions: region1 and region2, return the smallest region that contains both of them.
+It is guaranteed the smallest region exists.
+Example 1:
+Input:
+regions = [["Earth","North America","South America"],
+["North America","United States","Canada"],
+["United States","New York","Boston"],
+["Canada","Ontario","Quebec"],
+["South America","Brazil"]],
+region1 = "Quebec",
+region2 = "New York"
+Output: "North America"
+Example 2:
+Input: regions = [["Earth", "North America", "South America"],["North America", "United States", "Canada"],["United States", "New York", "Boston"],["Canada", "Ontario", "Quebec"],["South America", "Brazil"]], region1 = "Canada", region2 = "South America"
+Output: "Earth"
+Constraints:
+2 &lt;= regions.length &lt;= 104
+2 &lt;= regions[i].length &lt;= 20
+1 &lt;= regions[i][j].length, region1.length, region2.length &lt;= 20
+region1 != region2
+regions[i][j], region1, and region2 consist of English letters.
+The input is generated such that there exists a region which contains all the other regions, either directly or indirectly.
+A region cannot be directly contained in more than one region.</t>
+  </si>
+  <si>
+    <t>Maximum-Profit-in-Job-Scheduling</t>
+  </si>
+  <si>
+    <t>Maximum-Candies-You-Can-Get-from-Boxes</t>
+  </si>
+  <si>
+    <t>Smallest-Common-Region</t>
   </si>
 </sst>
 </file>
@@ -10818,10 +11410,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E3BD94-688A-45B7-B301-FA3F55251082}">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="1" max="1" width="38.21875" customWidth="1"/>
     <col min="2" max="2" width="37.109375" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" customWidth="1"/>
@@ -13738,10 +14330,10 @@
     </row>
     <row r="128" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>557</v>
+      </c>
+      <c r="B128" t="s">
         <v>558</v>
-      </c>
-      <c r="B128" t="s">
-        <v>559</v>
       </c>
       <c r="C128" t="s">
         <v>186</v>
@@ -13753,10 +14345,10 @@
         <v>187</v>
       </c>
       <c r="F128" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="G128" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>561</v>
       </c>
       <c r="H128" t="s">
         <v>480</v>
@@ -13764,10 +14356,10 @@
     </row>
     <row r="129" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>561</v>
+      </c>
+      <c r="B129" t="s">
         <v>562</v>
-      </c>
-      <c r="B129" t="s">
-        <v>563</v>
       </c>
       <c r="C129" t="s">
         <v>487</v>
@@ -13779,18 +14371,18 @@
         <v>487</v>
       </c>
       <c r="F129" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G129" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>565</v>
+      </c>
+      <c r="B130" t="s">
         <v>566</v>
-      </c>
-      <c r="B130" t="s">
-        <v>567</v>
       </c>
       <c r="C130" t="s">
         <v>487</v>
@@ -13802,18 +14394,18 @@
         <v>487</v>
       </c>
       <c r="F130" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G130" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>569</v>
+      </c>
+      <c r="B131" t="s">
         <v>570</v>
-      </c>
-      <c r="B131" t="s">
-        <v>571</v>
       </c>
       <c r="C131" t="s">
         <v>487</v>
@@ -13825,18 +14417,18 @@
         <v>487</v>
       </c>
       <c r="F131" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G131" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>573</v>
+      </c>
+      <c r="B132" t="s">
         <v>574</v>
-      </c>
-      <c r="B132" t="s">
-        <v>575</v>
       </c>
       <c r="C132" t="s">
         <v>487</v>
@@ -13848,18 +14440,18 @@
         <v>487</v>
       </c>
       <c r="F132" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G132" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>577</v>
+      </c>
+      <c r="B133" t="s">
         <v>578</v>
-      </c>
-      <c r="B133" t="s">
-        <v>579</v>
       </c>
       <c r="C133" t="s">
         <v>487</v>
@@ -13871,18 +14463,18 @@
         <v>487</v>
       </c>
       <c r="F133" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G133" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>581</v>
+      </c>
+      <c r="B134" t="s">
         <v>582</v>
-      </c>
-      <c r="B134" t="s">
-        <v>583</v>
       </c>
       <c r="C134" t="s">
         <v>487</v>
@@ -13894,18 +14486,18 @@
         <v>487</v>
       </c>
       <c r="F134" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="360" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>585</v>
+      </c>
+      <c r="B135" t="s">
         <v>586</v>
-      </c>
-      <c r="B135" t="s">
-        <v>587</v>
       </c>
       <c r="C135" t="s">
         <v>487</v>
@@ -13917,18 +14509,18 @@
         <v>487</v>
       </c>
       <c r="F135" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="G135" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>589</v>
+      </c>
+      <c r="B136" t="s">
         <v>590</v>
-      </c>
-      <c r="B136" t="s">
-        <v>591</v>
       </c>
       <c r="C136" t="s">
         <v>487</v>
@@ -13940,18 +14532,18 @@
         <v>487</v>
       </c>
       <c r="F136" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G136" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>595</v>
+      </c>
+      <c r="B137" t="s">
         <v>596</v>
-      </c>
-      <c r="B137" t="s">
-        <v>597</v>
       </c>
       <c r="C137" t="s">
         <v>11</v>
@@ -13960,21 +14552,21 @@
         <v>92</v>
       </c>
       <c r="E137" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>598</v>
+      </c>
+      <c r="B138" t="s">
         <v>599</v>
-      </c>
-      <c r="B138" t="s">
-        <v>600</v>
       </c>
       <c r="C138" t="s">
         <v>78</v>
@@ -13983,21 +14575,21 @@
         <v>92</v>
       </c>
       <c r="E138" t="s">
+        <v>600</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G138" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>603</v>
+      </c>
+      <c r="B139" t="s">
         <v>604</v>
-      </c>
-      <c r="B139" t="s">
-        <v>605</v>
       </c>
       <c r="C139" t="s">
         <v>78</v>
@@ -14006,21 +14598,21 @@
         <v>92</v>
       </c>
       <c r="E139" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>607</v>
+      </c>
+      <c r="B140" t="s">
         <v>608</v>
-      </c>
-      <c r="B140" t="s">
-        <v>609</v>
       </c>
       <c r="C140" t="s">
         <v>78</v>
@@ -14032,18 +14624,18 @@
         <v>78</v>
       </c>
       <c r="F140" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="G140" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>613</v>
+      </c>
+      <c r="B141" t="s">
         <v>614</v>
-      </c>
-      <c r="B141" t="s">
-        <v>615</v>
       </c>
       <c r="C141" t="s">
         <v>310</v>
@@ -14055,18 +14647,18 @@
         <v>310</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>617</v>
+      </c>
+      <c r="B142" t="s">
         <v>618</v>
-      </c>
-      <c r="B142" t="s">
-        <v>619</v>
       </c>
       <c r="C142" t="s">
         <v>532</v>
@@ -14078,18 +14670,18 @@
         <v>13</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>619</v>
+      </c>
+      <c r="B143" t="s">
         <v>620</v>
-      </c>
-      <c r="B143" t="s">
-        <v>621</v>
       </c>
       <c r="C143" t="s">
         <v>78</v>
@@ -14101,18 +14693,18 @@
         <v>78</v>
       </c>
       <c r="F143" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="G143" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>623</v>
+      </c>
+      <c r="B144" t="s">
         <v>624</v>
-      </c>
-      <c r="B144" t="s">
-        <v>625</v>
       </c>
       <c r="C144" t="s">
         <v>78</v>
@@ -14124,18 +14716,18 @@
         <v>78</v>
       </c>
       <c r="F144" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="G144" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>629</v>
+      </c>
+      <c r="B145" t="s">
         <v>630</v>
-      </c>
-      <c r="B145" t="s">
-        <v>631</v>
       </c>
       <c r="C145" t="s">
         <v>78</v>
@@ -14147,18 +14739,18 @@
         <v>78</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>631</v>
+      </c>
+      <c r="B146" t="s">
         <v>632</v>
-      </c>
-      <c r="B146" t="s">
-        <v>633</v>
       </c>
       <c r="C146" t="s">
         <v>78</v>
@@ -14170,18 +14762,18 @@
         <v>78</v>
       </c>
       <c r="F146" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="G146" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>635</v>
+      </c>
+      <c r="B147" t="s">
         <v>636</v>
-      </c>
-      <c r="B147" t="s">
-        <v>637</v>
       </c>
       <c r="C147" t="s">
         <v>11</v>
@@ -14193,18 +14785,18 @@
         <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>639</v>
+      </c>
+      <c r="B148" t="s">
         <v>640</v>
-      </c>
-      <c r="B148" t="s">
-        <v>641</v>
       </c>
       <c r="C148" t="s">
         <v>100</v>
@@ -14216,18 +14808,18 @@
         <v>100</v>
       </c>
       <c r="F148" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="G148" s="1" t="s">
         <v>642</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>643</v>
+      </c>
+      <c r="B149" t="s">
         <v>644</v>
-      </c>
-      <c r="B149" t="s">
-        <v>645</v>
       </c>
       <c r="C149" t="s">
         <v>460</v>
@@ -14240,15 +14832,15 @@
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>646</v>
+      </c>
+      <c r="B150" t="s">
         <v>647</v>
-      </c>
-      <c r="B150" t="s">
-        <v>648</v>
       </c>
       <c r="C150" t="s">
         <v>460</v>
@@ -14260,18 +14852,18 @@
         <v>460</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="G150" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>650</v>
+      </c>
+      <c r="B151" t="s">
         <v>651</v>
-      </c>
-      <c r="B151" t="s">
-        <v>652</v>
       </c>
       <c r="C151" t="s">
         <v>487</v>
@@ -14283,18 +14875,18 @@
         <v>487</v>
       </c>
       <c r="F151" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G151" s="1" t="s">
         <v>653</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>654</v>
+      </c>
+      <c r="B152" t="s">
         <v>655</v>
-      </c>
-      <c r="B152" t="s">
-        <v>656</v>
       </c>
       <c r="C152" t="s">
         <v>487</v>
@@ -14306,18 +14898,18 @@
         <v>487</v>
       </c>
       <c r="F152" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="G152" s="1" t="s">
         <v>657</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>658</v>
+      </c>
+      <c r="B153" t="s">
         <v>659</v>
-      </c>
-      <c r="B153" t="s">
-        <v>660</v>
       </c>
       <c r="C153" t="s">
         <v>487</v>
@@ -14329,18 +14921,18 @@
         <v>487</v>
       </c>
       <c r="F153" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G153" s="1" t="s">
         <v>661</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>662</v>
+      </c>
+      <c r="B154" t="s">
         <v>663</v>
-      </c>
-      <c r="B154" t="s">
-        <v>664</v>
       </c>
       <c r="C154" t="s">
         <v>78</v>
@@ -14352,18 +14944,18 @@
         <v>78</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>666</v>
+      </c>
+      <c r="B155" t="s">
         <v>667</v>
-      </c>
-      <c r="B155" t="s">
-        <v>668</v>
       </c>
       <c r="C155" t="s">
         <v>38</v>
@@ -14372,21 +14964,21 @@
         <v>12</v>
       </c>
       <c r="E155" t="s">
+        <v>668</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="G155" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>671</v>
+      </c>
+      <c r="B156" t="s">
         <v>672</v>
-      </c>
-      <c r="B156" t="s">
-        <v>673</v>
       </c>
       <c r="C156" t="s">
         <v>38</v>
@@ -14395,21 +14987,21 @@
         <v>25</v>
       </c>
       <c r="E156" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F156" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="G156" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>781</v>
+      </c>
+      <c r="B157" t="s">
         <v>782</v>
-      </c>
-      <c r="B157" t="s">
-        <v>783</v>
       </c>
       <c r="C157" t="s">
         <v>38</v>
@@ -14418,10 +15010,10 @@
         <v>25</v>
       </c>
       <c r="E157" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>40</v>
@@ -14429,10 +15021,10 @@
     </row>
     <row r="158" spans="1:7" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>676</v>
+      </c>
+      <c r="B158" t="s">
         <v>677</v>
-      </c>
-      <c r="B158" t="s">
-        <v>678</v>
       </c>
       <c r="C158" t="s">
         <v>38</v>
@@ -14441,21 +15033,21 @@
         <v>25</v>
       </c>
       <c r="E158" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F158" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="G158" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>680</v>
+      </c>
+      <c r="B159" t="s">
         <v>681</v>
-      </c>
-      <c r="B159" t="s">
-        <v>682</v>
       </c>
       <c r="C159" t="s">
         <v>38</v>
@@ -14464,21 +15056,21 @@
         <v>25</v>
       </c>
       <c r="E159" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F159" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="G159" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>684</v>
+      </c>
+      <c r="B160" t="s">
         <v>685</v>
-      </c>
-      <c r="B160" t="s">
-        <v>686</v>
       </c>
       <c r="C160" t="s">
         <v>38</v>
@@ -14487,21 +15079,21 @@
         <v>25</v>
       </c>
       <c r="E160" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F160" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="G160" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>688</v>
+      </c>
+      <c r="B161" t="s">
         <v>689</v>
-      </c>
-      <c r="B161" t="s">
-        <v>690</v>
       </c>
       <c r="C161" t="s">
         <v>38</v>
@@ -14510,21 +15102,21 @@
         <v>25</v>
       </c>
       <c r="E161" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F161" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="G161" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>692</v>
+      </c>
+      <c r="B162" t="s">
         <v>693</v>
-      </c>
-      <c r="B162" t="s">
-        <v>694</v>
       </c>
       <c r="C162" t="s">
         <v>38</v>
@@ -14533,21 +15125,21 @@
         <v>25</v>
       </c>
       <c r="E162" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F162" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="G162" s="1" t="s">
         <v>695</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>696</v>
+      </c>
+      <c r="B163" t="s">
         <v>697</v>
-      </c>
-      <c r="B163" t="s">
-        <v>698</v>
       </c>
       <c r="C163" t="s">
         <v>38</v>
@@ -14556,21 +15148,21 @@
         <v>25</v>
       </c>
       <c r="E163" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F163" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="G163" s="1" t="s">
         <v>699</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>700</v>
+      </c>
+      <c r="B164" t="s">
         <v>701</v>
-      </c>
-      <c r="B164" t="s">
-        <v>702</v>
       </c>
       <c r="C164" t="s">
         <v>38</v>
@@ -14579,21 +15171,21 @@
         <v>92</v>
       </c>
       <c r="E164" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F164" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="G164" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>704</v>
+      </c>
+      <c r="B165" t="s">
         <v>705</v>
-      </c>
-      <c r="B165" t="s">
-        <v>706</v>
       </c>
       <c r="C165" t="s">
         <v>38</v>
@@ -14602,21 +15194,21 @@
         <v>92</v>
       </c>
       <c r="E165" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F165" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="G165" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>708</v>
+      </c>
+      <c r="B166" t="s">
         <v>709</v>
-      </c>
-      <c r="B166" t="s">
-        <v>710</v>
       </c>
       <c r="C166" t="s">
         <v>186</v>
@@ -14628,18 +15220,18 @@
         <v>187</v>
       </c>
       <c r="F166" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="G166" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>712</v>
+      </c>
+      <c r="B167" t="s">
         <v>713</v>
-      </c>
-      <c r="B167" t="s">
-        <v>714</v>
       </c>
       <c r="C167" t="s">
         <v>78</v>
@@ -14651,18 +15243,18 @@
         <v>78</v>
       </c>
       <c r="F167" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="G167" s="1" t="s">
         <v>715</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>716</v>
+      </c>
+      <c r="B168" t="s">
         <v>717</v>
-      </c>
-      <c r="B168" t="s">
-        <v>718</v>
       </c>
       <c r="C168" t="s">
         <v>186</v>
@@ -14671,21 +15263,21 @@
         <v>92</v>
       </c>
       <c r="E168" t="s">
+        <v>718</v>
+      </c>
+      <c r="F168" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="F168" s="1" t="s">
+      <c r="G168" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>721</v>
+      </c>
+      <c r="B169" t="s">
         <v>722</v>
-      </c>
-      <c r="B169" t="s">
-        <v>723</v>
       </c>
       <c r="C169" t="s">
         <v>186</v>
@@ -14697,18 +15289,18 @@
         <v>200</v>
       </c>
       <c r="F169" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="G169" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>725</v>
+      </c>
+      <c r="B170" t="s">
         <v>726</v>
-      </c>
-      <c r="B170" t="s">
-        <v>727</v>
       </c>
       <c r="C170" t="s">
         <v>186</v>
@@ -14720,18 +15312,18 @@
         <v>222</v>
       </c>
       <c r="F170" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G170" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>729</v>
+      </c>
+      <c r="B171" t="s">
         <v>730</v>
-      </c>
-      <c r="B171" t="s">
-        <v>731</v>
       </c>
       <c r="C171" t="s">
         <v>292</v>
@@ -14740,21 +15332,21 @@
         <v>92</v>
       </c>
       <c r="E171" t="s">
+        <v>732</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G171" s="1" t="s">
         <v>733</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>734</v>
+      </c>
+      <c r="B172" t="s">
         <v>735</v>
-      </c>
-      <c r="B172" t="s">
-        <v>736</v>
       </c>
       <c r="C172" t="s">
         <v>292</v>
@@ -14763,21 +15355,21 @@
         <v>25</v>
       </c>
       <c r="E172" t="s">
+        <v>736</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="F172" s="1" t="s">
+      <c r="G172" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="360" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>739</v>
+      </c>
+      <c r="B173" t="s">
         <v>740</v>
-      </c>
-      <c r="B173" t="s">
-        <v>741</v>
       </c>
       <c r="C173" t="s">
         <v>292</v>
@@ -14786,21 +15378,21 @@
         <v>25</v>
       </c>
       <c r="E173" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F173" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="G173" s="1" t="s">
         <v>742</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>743</v>
+      </c>
+      <c r="B174" t="s">
         <v>744</v>
-      </c>
-      <c r="B174" t="s">
-        <v>745</v>
       </c>
       <c r="C174" t="s">
         <v>292</v>
@@ -14809,21 +15401,21 @@
         <v>25</v>
       </c>
       <c r="E174" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F174" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G174" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>747</v>
+      </c>
+      <c r="B175" t="s">
         <v>748</v>
-      </c>
-      <c r="B175" t="s">
-        <v>749</v>
       </c>
       <c r="C175" t="s">
         <v>292</v>
@@ -14832,21 +15424,21 @@
         <v>25</v>
       </c>
       <c r="E175" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>751</v>
+      </c>
+      <c r="B176" t="s">
         <v>752</v>
-      </c>
-      <c r="B176" t="s">
-        <v>753</v>
       </c>
       <c r="C176" t="s">
         <v>292</v>
@@ -14855,21 +15447,21 @@
         <v>25</v>
       </c>
       <c r="E176" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F176" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="G176" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>755</v>
+      </c>
+      <c r="B177" t="s">
         <v>756</v>
-      </c>
-      <c r="B177" t="s">
-        <v>757</v>
       </c>
       <c r="C177" t="s">
         <v>292</v>
@@ -14878,21 +15470,21 @@
         <v>25</v>
       </c>
       <c r="E177" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="360" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>760</v>
+      </c>
+      <c r="B178" t="s">
         <v>761</v>
-      </c>
-      <c r="B178" t="s">
-        <v>762</v>
       </c>
       <c r="C178" t="s">
         <v>434</v>
@@ -14901,21 +15493,21 @@
         <v>25</v>
       </c>
       <c r="E178" t="s">
+        <v>762</v>
+      </c>
+      <c r="F178" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="F178" s="1" t="s">
-        <v>764</v>
-      </c>
       <c r="G178" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>764</v>
+      </c>
+      <c r="B179" t="s">
         <v>765</v>
-      </c>
-      <c r="B179" t="s">
-        <v>766</v>
       </c>
       <c r="C179" t="s">
         <v>434</v>
@@ -14927,18 +15519,18 @@
         <v>434</v>
       </c>
       <c r="F179" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="G179" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>768</v>
+      </c>
+      <c r="B180" t="s">
         <v>769</v>
-      </c>
-      <c r="B180" t="s">
-        <v>770</v>
       </c>
       <c r="C180" t="s">
         <v>434</v>
@@ -14950,18 +15542,18 @@
         <v>542</v>
       </c>
       <c r="F180" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G180" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>772</v>
+      </c>
+      <c r="B181" t="s">
         <v>773</v>
-      </c>
-      <c r="B181" t="s">
-        <v>774</v>
       </c>
       <c r="C181" t="s">
         <v>434</v>
@@ -14973,18 +15565,18 @@
         <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="G181" s="1" t="s">
         <v>775</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>776</v>
+      </c>
+      <c r="B182" t="s">
         <v>777</v>
-      </c>
-      <c r="B182" t="s">
-        <v>778</v>
       </c>
       <c r="C182" t="s">
         <v>78</v>
@@ -14993,21 +15585,21 @@
         <v>92</v>
       </c>
       <c r="E182" t="s">
+        <v>778</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="G182" s="1" t="s">
         <v>780</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>783</v>
+      </c>
+      <c r="B183" t="s">
         <v>784</v>
-      </c>
-      <c r="B183" t="s">
-        <v>785</v>
       </c>
       <c r="C183" t="s">
         <v>292</v>
@@ -15019,18 +15611,18 @@
         <v>292</v>
       </c>
       <c r="F183" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="G183" s="1" t="s">
         <v>786</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>787</v>
+      </c>
+      <c r="B184" t="s">
         <v>788</v>
-      </c>
-      <c r="B184" t="s">
-        <v>789</v>
       </c>
       <c r="C184" t="s">
         <v>186</v>
@@ -15039,13 +15631,174 @@
         <v>92</v>
       </c>
       <c r="E184" t="s">
+        <v>789</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="F184" s="1" t="s">
+      <c r="G184" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="G184" s="1" t="s">
+    </row>
+    <row r="185" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>793</v>
+      </c>
+      <c r="B185" t="s">
+        <v>794</v>
+      </c>
+      <c r="C185" t="s">
+        <v>186</v>
+      </c>
+      <c r="D185" t="s">
+        <v>92</v>
+      </c>
+      <c r="E185" t="s">
+        <v>222</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="G185" s="1" t="s">
         <v>792</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>796</v>
+      </c>
+      <c r="B186" t="s">
+        <v>797</v>
+      </c>
+      <c r="C186" t="s">
+        <v>186</v>
+      </c>
+      <c r="D186" t="s">
+        <v>25</v>
+      </c>
+      <c r="E186" t="s">
+        <v>222</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>800</v>
+      </c>
+      <c r="B187" t="s">
+        <v>801</v>
+      </c>
+      <c r="C187" t="s">
+        <v>11</v>
+      </c>
+      <c r="D187" t="s">
+        <v>25</v>
+      </c>
+      <c r="E187" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>804</v>
+      </c>
+      <c r="B188" t="s">
+        <v>805</v>
+      </c>
+      <c r="C188" t="s">
+        <v>186</v>
+      </c>
+      <c r="D188" t="s">
+        <v>92</v>
+      </c>
+      <c r="E188" t="s">
+        <v>186</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>809</v>
+      </c>
+      <c r="B189" t="s">
+        <v>817</v>
+      </c>
+      <c r="C189" t="s">
+        <v>292</v>
+      </c>
+      <c r="D189" t="s">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>292</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>808</v>
+      </c>
+      <c r="B190" t="s">
+        <v>818</v>
+      </c>
+      <c r="C190" t="s">
+        <v>186</v>
+      </c>
+      <c r="D190" t="s">
+        <v>92</v>
+      </c>
+      <c r="E190" t="s">
+        <v>550</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>815</v>
+      </c>
+      <c r="B191" t="s">
+        <v>819</v>
+      </c>
+      <c r="C191" t="s">
+        <v>186</v>
+      </c>
+      <c r="D191" t="s">
+        <v>25</v>
+      </c>
+      <c r="E191" t="s">
+        <v>550</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -15059,16 +15812,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE6DFF0-2242-4479-B35B-6CF0472CBC8A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>557</v>
-      </c>
+      <c r="A1" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="https://leetcode.com/problems/escape-the-spreading-fire/" xr:uid="{1B9D0A80-0E75-49BE-A04F-97301E2C80A5}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>